--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N33_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>3.443129617684123</v>
       </c>
       <c r="E2" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F2" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>47.07755111555811</v>
       </c>
       <c r="E3" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F3" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>18.98847053151155</v>
       </c>
       <c r="E4" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F4" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>30.09572329777586</v>
       </c>
       <c r="E5" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F5" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>34.10143179813794</v>
       </c>
       <c r="E6" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F6" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>39.41951521744958</v>
       </c>
       <c r="E7" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F7" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>14.30448842025106</v>
       </c>
       <c r="E8" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F8" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>28.49530525413723</v>
       </c>
       <c r="E9" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F9" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>4.805914367799176</v>
       </c>
       <c r="E10" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F10" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         <v>12.06355371555338</v>
       </c>
       <c r="E11" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F11" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>7.529334794008744</v>
       </c>
       <c r="E12" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F12" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>12.85705029752023</v>
+        <v>13.24324682753259</v>
       </c>
       <c r="D13" t="n">
-        <v>12.16252044726406</v>
+        <v>12.86401393123656</v>
       </c>
       <c r="E13" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F13" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>24.64614122390743</v>
+        <v>12.85705029752023</v>
       </c>
       <c r="D14" t="n">
-        <v>25.59575789296495</v>
+        <v>12.16252044726406</v>
       </c>
       <c r="E14" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F14" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>17.45858997644049</v>
+        <v>24.64614122390743</v>
       </c>
       <c r="D15" t="n">
-        <v>17.01541443179784</v>
+        <v>25.59575789296495</v>
       </c>
       <c r="E15" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F15" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.90094356492943</v>
+        <v>17.45858997644049</v>
       </c>
       <c r="D16" t="n">
-        <v>32.29830610906902</v>
+        <v>17.01541443179784</v>
       </c>
       <c r="E16" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F16" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>16.35552424589386</v>
+        <v>31.90094356492943</v>
       </c>
       <c r="D17" t="n">
-        <v>9.569485601467983</v>
+        <v>32.29830610906902</v>
       </c>
       <c r="E17" t="n">
-        <v>14.9116129501856</v>
+        <v>14.65584855064744</v>
       </c>
       <c r="F17" t="n">
-        <v>12.58511028029197</v>
+        <v>12.35265620656162</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,23 +992,55 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
+        <v>16.35552424589386</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9.569485601467983</v>
+      </c>
+      <c r="E18" t="n">
+        <v>14.65584855064744</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12.35265620656162</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>T12594</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>W0065F0002T0006Z000C1N33.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="n">
         <v>1.688302563738246</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>10.31691185944515</v>
       </c>
-      <c r="E18" t="n">
-        <v>14.9116129501856</v>
-      </c>
-      <c r="F18" t="n">
-        <v>12.58511028029197</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>T12594</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="E19" t="n">
+        <v>14.65584855064744</v>
+      </c>
+      <c r="F19" t="n">
+        <v>12.35265620656162</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>T12594</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.933879399792237</v>
+        <v>0.6392554024662386</v>
       </c>
       <c r="D2" t="n">
-        <v>3.443129617684123</v>
+        <v>0.55950856287367</v>
       </c>
       <c r="E2" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F2" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.67443173141012</v>
+        <v>7.584595156354145</v>
       </c>
       <c r="D3" t="n">
-        <v>47.07755111555811</v>
+        <v>7.650102056278193</v>
       </c>
       <c r="E3" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F3" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.54325850582524</v>
+        <v>3.013279507196601</v>
       </c>
       <c r="D4" t="n">
-        <v>18.98847053151155</v>
+        <v>3.085626461370627</v>
       </c>
       <c r="E4" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F4" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.96739884285872</v>
+        <v>4.869702311964542</v>
       </c>
       <c r="D5" t="n">
-        <v>30.09572329777586</v>
+        <v>4.890555035888577</v>
       </c>
       <c r="E5" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F5" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.85212916689998</v>
+        <v>6.475970989621247</v>
       </c>
       <c r="D6" t="n">
-        <v>34.10143179813794</v>
+        <v>5.541482667197417</v>
       </c>
       <c r="E6" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F6" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.87435777905109</v>
+        <v>7.942083139095802</v>
       </c>
       <c r="D7" t="n">
-        <v>39.41951521744958</v>
+        <v>6.405671222835557</v>
       </c>
       <c r="E7" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F7" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.64104620265004</v>
+        <v>6.929170007930631</v>
       </c>
       <c r="D8" t="n">
-        <v>14.30448842025106</v>
+        <v>2.324479368290797</v>
       </c>
       <c r="E8" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F8" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.41652195986978</v>
+        <v>4.617684818478839</v>
       </c>
       <c r="D9" t="n">
-        <v>28.49530525413723</v>
+        <v>4.630487103797299</v>
       </c>
       <c r="E9" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F9" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>5.260251720300373</v>
+        <v>0.8547909045488107</v>
       </c>
       <c r="D10" t="n">
-        <v>4.805914367799176</v>
+        <v>0.780961084767366</v>
       </c>
       <c r="E10" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F10" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>11.83398395882463</v>
+        <v>1.923022393309002</v>
       </c>
       <c r="D11" t="n">
-        <v>12.06355371555338</v>
+        <v>1.960327478777425</v>
       </c>
       <c r="E11" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F11" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>6.674688279652941</v>
+        <v>1.084636845443603</v>
       </c>
       <c r="D12" t="n">
-        <v>7.529334794008744</v>
+        <v>1.223516904026421</v>
       </c>
       <c r="E12" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F12" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>13.24324682753259</v>
+        <v>2.152027609474045</v>
       </c>
       <c r="D13" t="n">
-        <v>12.86401393123656</v>
+        <v>2.09040226382594</v>
       </c>
       <c r="E13" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F13" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.85705029752023</v>
+        <v>2.089270673347038</v>
       </c>
       <c r="D14" t="n">
-        <v>12.16252044726406</v>
+        <v>1.976409572680409</v>
       </c>
       <c r="E14" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F14" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>24.64614122390743</v>
+        <v>4.004997948884957</v>
       </c>
       <c r="D15" t="n">
-        <v>25.59575789296495</v>
+        <v>4.159310657606804</v>
       </c>
       <c r="E15" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F15" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>17.45858997644049</v>
+        <v>2.837020871171579</v>
       </c>
       <c r="D16" t="n">
-        <v>17.01541443179784</v>
+        <v>2.765004845167149</v>
       </c>
       <c r="E16" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F16" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>31.90094356492943</v>
+        <v>5.183903329301033</v>
       </c>
       <c r="D17" t="n">
-        <v>32.29830610906902</v>
+        <v>5.248474742723715</v>
       </c>
       <c r="E17" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F17" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>16.35552424589386</v>
+        <v>2.657772689957752</v>
       </c>
       <c r="D18" t="n">
-        <v>9.569485601467983</v>
+        <v>1.555041410238547</v>
       </c>
       <c r="E18" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F18" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>1.688302563738246</v>
+        <v>0.274349166607465</v>
       </c>
       <c r="D19" t="n">
-        <v>10.31691185944515</v>
+        <v>1.676498177159837</v>
       </c>
       <c r="E19" t="n">
-        <v>14.65584855064744</v>
+        <v>2.381575389480209</v>
       </c>
       <c r="F19" t="n">
-        <v>12.35265620656162</v>
+        <v>2.007306633566264</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
